--- a/templates/HEM4_HAP_Emiss_ICF.xlsx
+++ b/templates/HEM4_HAP_Emiss_ICF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\55586\Desktop\tools\access tool\access-tool-migration\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DED411-4FDD-4BDB-B2B1-C41D14EC6FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11C8E36-343E-4904-B654-27BADB094FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4605" yWindow="4305" windowWidth="26265" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6465" yWindow="2130" windowWidth="26265" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hap emissions" sheetId="1" r:id="rId1"/>
@@ -130,17 +130,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -150,14 +151,24 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IQ214"/>
+  <dimension ref="A1:IQ298"/>
   <sheetFormatPr defaultColWidth="9.6640625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -494,19 +505,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:251" ht="51" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1"/>
@@ -756,7 +767,11 @@
       <c r="IQ1" s="1"/>
     </row>
     <row r="2" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D2" s="9"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -1004,7 +1019,11 @@
       <c r="IQ2" s="1"/>
     </row>
     <row r="3" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D3" s="9"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1252,7 +1271,11 @@
       <c r="IQ3" s="1"/>
     </row>
     <row r="4" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D4" s="9"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="13"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -1500,7 +1523,11 @@
       <c r="IQ4" s="1"/>
     </row>
     <row r="5" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D5" s="9"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1748,7 +1775,11 @@
       <c r="IQ5" s="1"/>
     </row>
     <row r="6" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D6" s="9"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1996,7 +2027,11 @@
       <c r="IQ6" s="1"/>
     </row>
     <row r="7" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D7" s="9"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -2244,7 +2279,11 @@
       <c r="IQ7" s="1"/>
     </row>
     <row r="8" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D8" s="9"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -2492,7 +2531,11 @@
       <c r="IQ8" s="1"/>
     </row>
     <row r="9" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D9" s="9"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -2740,7 +2783,11 @@
       <c r="IQ9" s="1"/>
     </row>
     <row r="10" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D10" s="9"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -2988,7 +3035,11 @@
       <c r="IQ10" s="1"/>
     </row>
     <row r="11" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D11" s="9"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -3236,7 +3287,11 @@
       <c r="IQ11" s="1"/>
     </row>
     <row r="12" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D12" s="9"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -3484,7 +3539,11 @@
       <c r="IQ12" s="1"/>
     </row>
     <row r="13" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D13" s="9"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -3732,7 +3791,11 @@
       <c r="IQ13" s="1"/>
     </row>
     <row r="14" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D14" s="9"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -3980,7 +4043,11 @@
       <c r="IQ14" s="1"/>
     </row>
     <row r="15" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D15" s="9"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -4228,7 +4295,11 @@
       <c r="IQ15" s="1"/>
     </row>
     <row r="16" spans="1:251" x14ac:dyDescent="0.2">
-      <c r="D16" s="9"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -4475,8 +4546,12 @@
       <c r="IP16" s="1"/>
       <c r="IQ16" s="1"/>
     </row>
-    <row r="17" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D17" s="9"/>
+    <row r="17" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -4723,8 +4798,12 @@
       <c r="IP17" s="1"/>
       <c r="IQ17" s="1"/>
     </row>
-    <row r="18" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D18" s="9"/>
+    <row r="18" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -4971,8 +5050,12 @@
       <c r="IP18" s="1"/>
       <c r="IQ18" s="1"/>
     </row>
-    <row r="19" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D19" s="9"/>
+    <row r="19" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -5219,8 +5302,12 @@
       <c r="IP19" s="1"/>
       <c r="IQ19" s="1"/>
     </row>
-    <row r="20" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D20" s="9"/>
+    <row r="20" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="13"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -5467,8 +5554,12 @@
       <c r="IP20" s="1"/>
       <c r="IQ20" s="1"/>
     </row>
-    <row r="21" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D21" s="9"/>
+    <row r="21" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -5715,8 +5806,12 @@
       <c r="IP21" s="1"/>
       <c r="IQ21" s="1"/>
     </row>
-    <row r="22" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D22" s="9"/>
+    <row r="22" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="13"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5963,8 +6058,12 @@
       <c r="IP22" s="1"/>
       <c r="IQ22" s="1"/>
     </row>
-    <row r="23" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D23" s="9"/>
+    <row r="23" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="13"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -6211,8 +6310,12 @@
       <c r="IP23" s="1"/>
       <c r="IQ23" s="1"/>
     </row>
-    <row r="24" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D24" s="9"/>
+    <row r="24" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="13"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -6459,8 +6562,12 @@
       <c r="IP24" s="1"/>
       <c r="IQ24" s="1"/>
     </row>
-    <row r="25" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D25" s="9"/>
+    <row r="25" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -6707,8 +6814,12 @@
       <c r="IP25" s="1"/>
       <c r="IQ25" s="1"/>
     </row>
-    <row r="26" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D26" s="9"/>
+    <row r="26" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="13"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -6955,8 +7066,12 @@
       <c r="IP26" s="1"/>
       <c r="IQ26" s="1"/>
     </row>
-    <row r="27" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D27" s="9"/>
+    <row r="27" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="13"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -7203,8 +7318,12 @@
       <c r="IP27" s="1"/>
       <c r="IQ27" s="1"/>
     </row>
-    <row r="28" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D28" s="9"/>
+    <row r="28" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="13"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -7451,8 +7570,12 @@
       <c r="IP28" s="1"/>
       <c r="IQ28" s="1"/>
     </row>
-    <row r="29" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D29" s="9"/>
+    <row r="29" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="13"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -7699,8 +7822,12 @@
       <c r="IP29" s="1"/>
       <c r="IQ29" s="1"/>
     </row>
-    <row r="30" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D30" s="9"/>
+    <row r="30" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="13"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -7947,8 +8074,12 @@
       <c r="IP30" s="1"/>
       <c r="IQ30" s="1"/>
     </row>
-    <row r="31" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D31" s="9"/>
+    <row r="31" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="13"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -8195,8 +8326,12 @@
       <c r="IP31" s="1"/>
       <c r="IQ31" s="1"/>
     </row>
-    <row r="32" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D32" s="9"/>
+    <row r="32" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="13"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -8443,8 +8578,12 @@
       <c r="IP32" s="1"/>
       <c r="IQ32" s="1"/>
     </row>
-    <row r="33" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D33" s="9"/>
+    <row r="33" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="13"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -8691,8 +8830,12 @@
       <c r="IP33" s="1"/>
       <c r="IQ33" s="1"/>
     </row>
-    <row r="34" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D34" s="9"/>
+    <row r="34" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="13"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -8939,8 +9082,12 @@
       <c r="IP34" s="1"/>
       <c r="IQ34" s="1"/>
     </row>
-    <row r="35" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D35" s="9"/>
+    <row r="35" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="13"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -9187,8 +9334,12 @@
       <c r="IP35" s="1"/>
       <c r="IQ35" s="1"/>
     </row>
-    <row r="36" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D36" s="9"/>
+    <row r="36" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="13"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -9435,8 +9586,12 @@
       <c r="IP36" s="1"/>
       <c r="IQ36" s="1"/>
     </row>
-    <row r="37" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D37" s="9"/>
+    <row r="37" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="13"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -9683,8 +9838,12 @@
       <c r="IP37" s="1"/>
       <c r="IQ37" s="1"/>
     </row>
-    <row r="38" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D38" s="9"/>
+    <row r="38" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="13"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -9931,8 +10090,12 @@
       <c r="IP38" s="1"/>
       <c r="IQ38" s="1"/>
     </row>
-    <row r="39" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D39" s="9"/>
+    <row r="39" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="13"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -10179,8 +10342,12 @@
       <c r="IP39" s="1"/>
       <c r="IQ39" s="1"/>
     </row>
-    <row r="40" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D40" s="9"/>
+    <row r="40" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="13"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -10427,129 +10594,264 @@
       <c r="IP40" s="1"/>
       <c r="IQ40" s="1"/>
     </row>
-    <row r="41" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D41" s="9"/>
-    </row>
-    <row r="42" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D42" s="9"/>
-    </row>
-    <row r="43" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-    </row>
-    <row r="44" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D44" s="9"/>
-    </row>
-    <row r="45" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D45" s="9"/>
-    </row>
-    <row r="46" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D46" s="9"/>
-    </row>
-    <row r="47" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D47" s="9"/>
-    </row>
-    <row r="48" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D48" s="9"/>
-    </row>
-    <row r="49" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D49" s="9"/>
-    </row>
-    <row r="50" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D50" s="9"/>
-    </row>
-    <row r="51" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D51" s="9"/>
-    </row>
-    <row r="52" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D52" s="9"/>
-      <c r="E52" s="10"/>
-    </row>
-    <row r="53" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D53" s="9"/>
-      <c r="E53" s="10"/>
-    </row>
-    <row r="54" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-    </row>
-    <row r="55" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D55" s="9"/>
-      <c r="E55" s="10"/>
-    </row>
-    <row r="56" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D56" s="9"/>
-      <c r="E56" s="11"/>
-    </row>
-    <row r="57" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D57" s="9"/>
-      <c r="E57" s="11"/>
-    </row>
-    <row r="58" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D58" s="9"/>
-      <c r="E58" s="11"/>
-    </row>
-    <row r="59" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D59" s="9"/>
-      <c r="E59" s="11"/>
-    </row>
-    <row r="60" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D60" s="9"/>
-    </row>
-    <row r="61" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D61" s="9"/>
-    </row>
-    <row r="62" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D62" s="9"/>
-    </row>
-    <row r="63" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D63" s="9"/>
-    </row>
-    <row r="64" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D64" s="9"/>
-    </row>
-    <row r="65" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D65" s="9"/>
-    </row>
-    <row r="66" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D66" s="9"/>
-    </row>
-    <row r="67" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D67" s="9"/>
-    </row>
-    <row r="68" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D68" s="9"/>
-    </row>
-    <row r="69" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D69" s="9"/>
-    </row>
-    <row r="70" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D70" s="9"/>
-    </row>
-    <row r="71" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D71" s="9"/>
-    </row>
-    <row r="72" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D72" s="9"/>
-      <c r="E72" s="10"/>
-    </row>
-    <row r="73" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D73" s="9"/>
-      <c r="E73" s="10"/>
-    </row>
-    <row r="74" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D74" s="9"/>
-      <c r="E74" s="10"/>
-    </row>
-    <row r="75" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D75" s="9"/>
-      <c r="E75" s="10"/>
-    </row>
-    <row r="76" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D76" s="9"/>
-    </row>
-    <row r="77" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D77" s="9"/>
+    <row r="41" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="13"/>
+    </row>
+    <row r="42" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="13"/>
+    </row>
+    <row r="43" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="14"/>
+    </row>
+    <row r="44" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="13"/>
+    </row>
+    <row r="45" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A45" s="11"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="13"/>
+    </row>
+    <row r="46" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="13"/>
+    </row>
+    <row r="47" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="13"/>
+    </row>
+    <row r="48" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="13"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="13"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="13"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="13"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="11"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="14"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="14"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="14"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="14"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="15"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="15"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="11"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="15"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="15"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="13"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="13"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="11"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="13"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="13"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="11"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="13"/>
+    </row>
+    <row r="65" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="13"/>
+    </row>
+    <row r="66" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="13"/>
+    </row>
+    <row r="67" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="13"/>
+    </row>
+    <row r="68" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A68" s="11"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="13"/>
+    </row>
+    <row r="69" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A69" s="11"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="13"/>
+    </row>
+    <row r="70" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A70" s="11"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="13"/>
+    </row>
+    <row r="71" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="13"/>
+    </row>
+    <row r="72" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A72" s="11"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="14"/>
+    </row>
+    <row r="73" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A73" s="11"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="14"/>
+    </row>
+    <row r="74" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A74" s="11"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="14"/>
+    </row>
+    <row r="75" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A75" s="11"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="14"/>
+    </row>
+    <row r="76" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A76" s="11"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="13"/>
+    </row>
+    <row r="77" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A77" s="11"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="13"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -10796,8 +11098,12 @@
       <c r="IP77" s="1"/>
       <c r="IQ77" s="1"/>
     </row>
-    <row r="78" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D78" s="9"/>
+    <row r="78" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A78" s="11"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="13"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -11044,8 +11350,12 @@
       <c r="IP78" s="1"/>
       <c r="IQ78" s="1"/>
     </row>
-    <row r="79" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D79" s="9"/>
+    <row r="79" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A79" s="11"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="13"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -11292,8 +11602,12 @@
       <c r="IP79" s="1"/>
       <c r="IQ79" s="1"/>
     </row>
-    <row r="80" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D80" s="9"/>
+    <row r="80" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A80" s="11"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="13"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -11540,8 +11854,12 @@
       <c r="IP80" s="1"/>
       <c r="IQ80" s="1"/>
     </row>
-    <row r="81" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D81" s="9"/>
+    <row r="81" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A81" s="11"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="13"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -11788,8 +12106,12 @@
       <c r="IP81" s="1"/>
       <c r="IQ81" s="1"/>
     </row>
-    <row r="82" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D82" s="9"/>
+    <row r="82" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A82" s="11"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="13"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -12036,8 +12358,12 @@
       <c r="IP82" s="1"/>
       <c r="IQ82" s="1"/>
     </row>
-    <row r="83" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D83" s="9"/>
+    <row r="83" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A83" s="11"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="13"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -12284,8 +12610,12 @@
       <c r="IP83" s="1"/>
       <c r="IQ83" s="1"/>
     </row>
-    <row r="84" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D84" s="9"/>
+    <row r="84" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A84" s="11"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="13"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -12532,8 +12862,12 @@
       <c r="IP84" s="1"/>
       <c r="IQ84" s="1"/>
     </row>
-    <row r="85" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D85" s="9"/>
+    <row r="85" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A85" s="11"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="13"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -12780,8 +13114,12 @@
       <c r="IP85" s="1"/>
       <c r="IQ85" s="1"/>
     </row>
-    <row r="86" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D86" s="9"/>
+    <row r="86" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A86" s="11"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="13"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -13028,8 +13366,12 @@
       <c r="IP86" s="1"/>
       <c r="IQ86" s="1"/>
     </row>
-    <row r="87" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D87" s="9"/>
+    <row r="87" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A87" s="11"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="13"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -13276,8 +13618,12 @@
       <c r="IP87" s="1"/>
       <c r="IQ87" s="1"/>
     </row>
-    <row r="88" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D88" s="9"/>
+    <row r="88" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A88" s="11"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="13"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -13524,8 +13870,12 @@
       <c r="IP88" s="1"/>
       <c r="IQ88" s="1"/>
     </row>
-    <row r="89" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D89" s="9"/>
+    <row r="89" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A89" s="11"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="12"/>
+      <c r="E89" s="13"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -13772,8 +14122,12 @@
       <c r="IP89" s="1"/>
       <c r="IQ89" s="1"/>
     </row>
-    <row r="90" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D90" s="9"/>
+    <row r="90" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A90" s="11"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="13"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -14020,8 +14374,12 @@
       <c r="IP90" s="1"/>
       <c r="IQ90" s="1"/>
     </row>
-    <row r="91" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D91" s="9"/>
+    <row r="91" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A91" s="11"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="13"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -14268,375 +14626,1286 @@
       <c r="IP91" s="1"/>
       <c r="IQ91" s="1"/>
     </row>
-    <row r="92" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D92" s="9"/>
-    </row>
-    <row r="93" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D93" s="9"/>
-    </row>
-    <row r="94" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D94" s="9"/>
-      <c r="E94" s="10"/>
-    </row>
-    <row r="95" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D95" s="9"/>
-    </row>
-    <row r="96" spans="4:251" x14ac:dyDescent="0.2">
-      <c r="D96" s="9"/>
-    </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D97" s="9"/>
-    </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D98" s="9"/>
-    </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D99" s="9"/>
-    </row>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D100" s="9"/>
-    </row>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D101" s="9"/>
-    </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D102" s="9"/>
-    </row>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D103" s="9"/>
-    </row>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D104" s="9"/>
-    </row>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D105" s="9"/>
-    </row>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D106" s="9"/>
-    </row>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D107" s="9"/>
-    </row>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D108" s="9"/>
-    </row>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D109" s="9"/>
-    </row>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D110" s="9"/>
-    </row>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D111" s="9"/>
-    </row>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D112" s="9"/>
-    </row>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D113" s="9"/>
-    </row>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D114" s="9"/>
-    </row>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D115" s="9"/>
-    </row>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D116" s="9"/>
-    </row>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D117" s="9"/>
-    </row>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D118" s="9"/>
-    </row>
-    <row r="119" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D119" s="9"/>
-    </row>
-    <row r="120" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D120" s="9"/>
-    </row>
-    <row r="121" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D121" s="9"/>
-    </row>
-    <row r="122" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D122" s="9"/>
-    </row>
-    <row r="123" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D123" s="9"/>
-    </row>
-    <row r="124" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D124" s="9"/>
-    </row>
-    <row r="125" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D125" s="9"/>
-    </row>
-    <row r="126" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D126" s="9"/>
-    </row>
-    <row r="127" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D127" s="9"/>
-    </row>
-    <row r="128" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D128" s="9"/>
-    </row>
-    <row r="129" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D129" s="9"/>
-    </row>
-    <row r="130" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D130" s="9"/>
-    </row>
-    <row r="131" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D131" s="9"/>
-    </row>
-    <row r="132" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D132" s="9"/>
-    </row>
-    <row r="133" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D133" s="9"/>
-    </row>
-    <row r="134" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D134" s="9"/>
-    </row>
-    <row r="135" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D135" s="9"/>
-    </row>
-    <row r="136" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D136" s="9"/>
-    </row>
-    <row r="137" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D137" s="9"/>
-    </row>
-    <row r="138" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D138" s="9"/>
-    </row>
-    <row r="139" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D139" s="9"/>
-    </row>
-    <row r="140" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D140" s="9"/>
-    </row>
-    <row r="141" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D141" s="9"/>
-    </row>
-    <row r="142" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D142" s="9"/>
-    </row>
-    <row r="143" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D143" s="9"/>
-    </row>
-    <row r="144" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D144" s="9"/>
-    </row>
-    <row r="145" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D145" s="9"/>
-    </row>
-    <row r="146" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D146" s="9"/>
-    </row>
-    <row r="147" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D147" s="9"/>
-    </row>
-    <row r="148" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D148" s="9"/>
-    </row>
-    <row r="149" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D149" s="9"/>
-    </row>
-    <row r="150" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D150" s="9"/>
-    </row>
-    <row r="151" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D151" s="9"/>
-    </row>
-    <row r="152" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D152" s="9"/>
-    </row>
-    <row r="153" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D153" s="9"/>
-    </row>
-    <row r="154" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D154" s="9"/>
-    </row>
-    <row r="155" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D155" s="9"/>
-    </row>
-    <row r="156" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D156" s="9"/>
-    </row>
-    <row r="157" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D157" s="9"/>
-    </row>
-    <row r="158" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D158" s="9"/>
-    </row>
-    <row r="159" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D159" s="9"/>
-    </row>
-    <row r="160" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D160" s="9"/>
-    </row>
-    <row r="161" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D161" s="9"/>
-    </row>
-    <row r="162" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D162" s="9"/>
-    </row>
-    <row r="163" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D163" s="9"/>
-    </row>
-    <row r="164" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D164" s="9"/>
-    </row>
-    <row r="165" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D165" s="9"/>
-    </row>
-    <row r="166" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D166" s="9"/>
-    </row>
-    <row r="167" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D167" s="9"/>
-    </row>
-    <row r="168" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D168" s="9"/>
-    </row>
-    <row r="169" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D169" s="9"/>
-    </row>
-    <row r="170" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D170" s="9"/>
-    </row>
-    <row r="171" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D171" s="9"/>
-    </row>
-    <row r="172" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D172" s="9"/>
-    </row>
-    <row r="173" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D173" s="9"/>
-    </row>
-    <row r="174" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D174" s="9"/>
-    </row>
-    <row r="175" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D175" s="9"/>
-    </row>
-    <row r="176" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D176" s="9"/>
-    </row>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D177" s="9"/>
-    </row>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D178" s="9"/>
-    </row>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D179" s="9"/>
-    </row>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D180" s="9"/>
-    </row>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D181" s="9"/>
-    </row>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D182" s="9"/>
-    </row>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D183" s="9"/>
-    </row>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D184" s="9"/>
-    </row>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D185" s="9"/>
-    </row>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D186" s="9"/>
-    </row>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D187" s="9"/>
-    </row>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D188" s="9"/>
-    </row>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D189" s="9"/>
-    </row>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D190" s="9"/>
-    </row>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D191" s="9"/>
-    </row>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D192" s="9"/>
-    </row>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D193" s="9"/>
-    </row>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D194" s="9"/>
-    </row>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D195" s="9"/>
-    </row>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D196" s="9"/>
-    </row>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D197" s="9"/>
-    </row>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D198" s="9"/>
-    </row>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D199" s="9"/>
-    </row>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D200" s="9"/>
-    </row>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D201" s="9"/>
-    </row>
-    <row r="202" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D202" s="9"/>
-    </row>
-    <row r="203" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D203" s="9"/>
-    </row>
-    <row r="204" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D204" s="9"/>
-    </row>
-    <row r="205" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D205" s="9"/>
-    </row>
-    <row r="206" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D206" s="9"/>
-    </row>
-    <row r="207" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D207" s="9"/>
-    </row>
-    <row r="208" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D208" s="9"/>
-    </row>
-    <row r="209" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D209" s="9"/>
-    </row>
-    <row r="210" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D210" s="9"/>
-    </row>
-    <row r="211" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D211" s="9"/>
-    </row>
-    <row r="212" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D212" s="9"/>
-    </row>
-    <row r="213" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D213" s="9"/>
-    </row>
-    <row r="214" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D214" s="9"/>
+    <row r="92" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A92" s="11"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="13"/>
+    </row>
+    <row r="93" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A93" s="11"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="13"/>
+    </row>
+    <row r="94" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A94" s="11"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="14"/>
+    </row>
+    <row r="95" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A95" s="11"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="13"/>
+    </row>
+    <row r="96" spans="1:251" x14ac:dyDescent="0.2">
+      <c r="A96" s="11"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="13"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="11"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="13"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="11"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="13"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="11"/>
+      <c r="B99" s="11"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="13"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="11"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="13"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="11"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="12"/>
+      <c r="E101" s="13"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="11"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="13"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="11"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="12"/>
+      <c r="E103" s="16"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="11"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="12"/>
+      <c r="E104" s="16"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="11"/>
+      <c r="B105" s="11"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="12"/>
+      <c r="E105" s="16"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="11"/>
+      <c r="B106" s="11"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="16"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="11"/>
+      <c r="B107" s="11"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="16"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="11"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="16"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="11"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="12"/>
+      <c r="E109" s="16"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="11"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="12"/>
+      <c r="E110" s="16"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="11"/>
+      <c r="B111" s="11"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="16"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="11"/>
+      <c r="B112" s="11"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="12"/>
+      <c r="E112" s="16"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="11"/>
+      <c r="B113" s="11"/>
+      <c r="C113" s="5"/>
+      <c r="D113" s="12"/>
+      <c r="E113" s="16"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="11"/>
+      <c r="B114" s="11"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="12"/>
+      <c r="E114" s="16"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="11"/>
+      <c r="B115" s="11"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="16"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="11"/>
+      <c r="B116" s="11"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="12"/>
+      <c r="E116" s="16"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="11"/>
+      <c r="B117" s="11"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="16"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="11"/>
+      <c r="B118" s="11"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="12"/>
+      <c r="E118" s="16"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="11"/>
+      <c r="B119" s="11"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="16"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" s="11"/>
+      <c r="B120" s="11"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="12"/>
+      <c r="E120" s="16"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="11"/>
+      <c r="B121" s="11"/>
+      <c r="C121" s="5"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="16"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" s="11"/>
+      <c r="B122" s="11"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="12"/>
+      <c r="E122" s="16"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" s="11"/>
+      <c r="B123" s="11"/>
+      <c r="C123" s="5"/>
+      <c r="D123" s="12"/>
+      <c r="E123" s="16"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="11"/>
+      <c r="B124" s="11"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="12"/>
+      <c r="E124" s="16"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="11"/>
+      <c r="B125" s="11"/>
+      <c r="C125" s="5"/>
+      <c r="D125" s="12"/>
+      <c r="E125" s="16"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" s="11"/>
+      <c r="B126" s="11"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="12"/>
+      <c r="E126" s="16"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" s="11"/>
+      <c r="B127" s="11"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="12"/>
+      <c r="E127" s="16"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" s="11"/>
+      <c r="B128" s="11"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="12"/>
+      <c r="E128" s="16"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" s="11"/>
+      <c r="B129" s="11"/>
+      <c r="C129" s="5"/>
+      <c r="D129" s="12"/>
+      <c r="E129" s="16"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" s="11"/>
+      <c r="B130" s="11"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="16"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" s="11"/>
+      <c r="B131" s="11"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="12"/>
+      <c r="E131" s="16"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" s="11"/>
+      <c r="B132" s="11"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="12"/>
+      <c r="E132" s="16"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" s="11"/>
+      <c r="B133" s="11"/>
+      <c r="C133" s="5"/>
+      <c r="D133" s="12"/>
+      <c r="E133" s="16"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134" s="11"/>
+      <c r="B134" s="11"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="12"/>
+      <c r="E134" s="16"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" s="11"/>
+      <c r="B135" s="11"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="12"/>
+      <c r="E135" s="16"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136" s="11"/>
+      <c r="B136" s="11"/>
+      <c r="C136" s="5"/>
+      <c r="D136" s="12"/>
+      <c r="E136" s="16"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137" s="11"/>
+      <c r="B137" s="11"/>
+      <c r="C137" s="5"/>
+      <c r="D137" s="12"/>
+      <c r="E137" s="16"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" s="11"/>
+      <c r="B138" s="11"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="12"/>
+      <c r="E138" s="16"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" s="11"/>
+      <c r="B139" s="11"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="12"/>
+      <c r="E139" s="16"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" s="11"/>
+      <c r="B140" s="11"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="12"/>
+      <c r="E140" s="16"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" s="11"/>
+      <c r="B141" s="11"/>
+      <c r="C141" s="5"/>
+      <c r="D141" s="12"/>
+      <c r="E141" s="16"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" s="11"/>
+      <c r="B142" s="11"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="12"/>
+      <c r="E142" s="16"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143" s="11"/>
+      <c r="B143" s="11"/>
+      <c r="C143" s="5"/>
+      <c r="D143" s="12"/>
+      <c r="E143" s="16"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144" s="11"/>
+      <c r="B144" s="11"/>
+      <c r="C144" s="5"/>
+      <c r="D144" s="12"/>
+      <c r="E144" s="16"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145" s="11"/>
+      <c r="B145" s="11"/>
+      <c r="C145" s="5"/>
+      <c r="D145" s="12"/>
+      <c r="E145" s="16"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146" s="11"/>
+      <c r="B146" s="11"/>
+      <c r="C146" s="5"/>
+      <c r="D146" s="12"/>
+      <c r="E146" s="16"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147" s="11"/>
+      <c r="B147" s="11"/>
+      <c r="C147" s="5"/>
+      <c r="D147" s="12"/>
+      <c r="E147" s="16"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148" s="11"/>
+      <c r="B148" s="11"/>
+      <c r="C148" s="5"/>
+      <c r="D148" s="12"/>
+      <c r="E148" s="16"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" s="11"/>
+      <c r="B149" s="11"/>
+      <c r="C149" s="5"/>
+      <c r="D149" s="12"/>
+      <c r="E149" s="16"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A150" s="11"/>
+      <c r="B150" s="11"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="12"/>
+      <c r="E150" s="16"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151" s="11"/>
+      <c r="B151" s="11"/>
+      <c r="C151" s="5"/>
+      <c r="D151" s="12"/>
+      <c r="E151" s="16"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152" s="11"/>
+      <c r="B152" s="11"/>
+      <c r="C152" s="5"/>
+      <c r="D152" s="12"/>
+      <c r="E152" s="16"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" s="11"/>
+      <c r="B153" s="11"/>
+      <c r="C153" s="5"/>
+      <c r="D153" s="12"/>
+      <c r="E153" s="16"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154" s="11"/>
+      <c r="B154" s="11"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="12"/>
+      <c r="E154" s="16"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" s="11"/>
+      <c r="B155" s="11"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="12"/>
+      <c r="E155" s="16"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" s="11"/>
+      <c r="B156" s="11"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="12"/>
+      <c r="E156" s="16"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A157" s="11"/>
+      <c r="B157" s="11"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="12"/>
+      <c r="E157" s="16"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A158" s="11"/>
+      <c r="B158" s="11"/>
+      <c r="C158" s="5"/>
+      <c r="D158" s="12"/>
+      <c r="E158" s="16"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159" s="11"/>
+      <c r="B159" s="11"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="12"/>
+      <c r="E159" s="16"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A160" s="11"/>
+      <c r="B160" s="11"/>
+      <c r="C160" s="5"/>
+      <c r="D160" s="12"/>
+      <c r="E160" s="16"/>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A161" s="11"/>
+      <c r="B161" s="11"/>
+      <c r="C161" s="5"/>
+      <c r="D161" s="12"/>
+      <c r="E161" s="16"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A162" s="11"/>
+      <c r="B162" s="11"/>
+      <c r="C162" s="5"/>
+      <c r="D162" s="12"/>
+      <c r="E162" s="16"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A163" s="11"/>
+      <c r="B163" s="11"/>
+      <c r="C163" s="5"/>
+      <c r="D163" s="12"/>
+      <c r="E163" s="16"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A164" s="11"/>
+      <c r="B164" s="11"/>
+      <c r="C164" s="5"/>
+      <c r="D164" s="12"/>
+      <c r="E164" s="16"/>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A165" s="11"/>
+      <c r="B165" s="11"/>
+      <c r="C165" s="5"/>
+      <c r="D165" s="12"/>
+      <c r="E165" s="16"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A166" s="11"/>
+      <c r="B166" s="11"/>
+      <c r="C166" s="5"/>
+      <c r="D166" s="12"/>
+      <c r="E166" s="16"/>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A167" s="11"/>
+      <c r="B167" s="11"/>
+      <c r="C167" s="5"/>
+      <c r="D167" s="12"/>
+      <c r="E167" s="16"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A168" s="11"/>
+      <c r="B168" s="11"/>
+      <c r="C168" s="5"/>
+      <c r="D168" s="12"/>
+      <c r="E168" s="16"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A169" s="11"/>
+      <c r="B169" s="11"/>
+      <c r="C169" s="5"/>
+      <c r="D169" s="12"/>
+      <c r="E169" s="16"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A170" s="11"/>
+      <c r="B170" s="11"/>
+      <c r="C170" s="5"/>
+      <c r="D170" s="12"/>
+      <c r="E170" s="16"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A171" s="11"/>
+      <c r="B171" s="11"/>
+      <c r="C171" s="5"/>
+      <c r="D171" s="12"/>
+      <c r="E171" s="16"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A172" s="11"/>
+      <c r="B172" s="11"/>
+      <c r="C172" s="5"/>
+      <c r="D172" s="12"/>
+      <c r="E172" s="16"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A173" s="11"/>
+      <c r="B173" s="11"/>
+      <c r="C173" s="5"/>
+      <c r="D173" s="12"/>
+      <c r="E173" s="16"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A174" s="11"/>
+      <c r="B174" s="11"/>
+      <c r="C174" s="5"/>
+      <c r="D174" s="12"/>
+      <c r="E174" s="16"/>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A175" s="11"/>
+      <c r="B175" s="11"/>
+      <c r="C175" s="5"/>
+      <c r="D175" s="12"/>
+      <c r="E175" s="16"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A176" s="11"/>
+      <c r="B176" s="11"/>
+      <c r="C176" s="5"/>
+      <c r="D176" s="12"/>
+      <c r="E176" s="16"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A177" s="11"/>
+      <c r="B177" s="11"/>
+      <c r="C177" s="5"/>
+      <c r="D177" s="12"/>
+      <c r="E177" s="16"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A178" s="11"/>
+      <c r="B178" s="11"/>
+      <c r="C178" s="5"/>
+      <c r="D178" s="12"/>
+      <c r="E178" s="16"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A179" s="11"/>
+      <c r="B179" s="11"/>
+      <c r="C179" s="5"/>
+      <c r="D179" s="12"/>
+      <c r="E179" s="16"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A180" s="11"/>
+      <c r="B180" s="11"/>
+      <c r="C180" s="5"/>
+      <c r="D180" s="12"/>
+      <c r="E180" s="16"/>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A181" s="11"/>
+      <c r="B181" s="11"/>
+      <c r="C181" s="5"/>
+      <c r="D181" s="12"/>
+      <c r="E181" s="16"/>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A182" s="11"/>
+      <c r="B182" s="11"/>
+      <c r="C182" s="5"/>
+      <c r="D182" s="12"/>
+      <c r="E182" s="16"/>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A183" s="11"/>
+      <c r="B183" s="11"/>
+      <c r="C183" s="5"/>
+      <c r="D183" s="12"/>
+      <c r="E183" s="16"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A184" s="11"/>
+      <c r="B184" s="11"/>
+      <c r="C184" s="5"/>
+      <c r="D184" s="12"/>
+      <c r="E184" s="16"/>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A185" s="11"/>
+      <c r="B185" s="11"/>
+      <c r="C185" s="5"/>
+      <c r="D185" s="12"/>
+      <c r="E185" s="16"/>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A186" s="11"/>
+      <c r="B186" s="11"/>
+      <c r="C186" s="5"/>
+      <c r="D186" s="12"/>
+      <c r="E186" s="16"/>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A187" s="11"/>
+      <c r="B187" s="11"/>
+      <c r="C187" s="5"/>
+      <c r="D187" s="12"/>
+      <c r="E187" s="16"/>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A188" s="11"/>
+      <c r="B188" s="11"/>
+      <c r="C188" s="5"/>
+      <c r="D188" s="12"/>
+      <c r="E188" s="16"/>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A189" s="11"/>
+      <c r="B189" s="11"/>
+      <c r="C189" s="5"/>
+      <c r="D189" s="12"/>
+      <c r="E189" s="16"/>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A190" s="11"/>
+      <c r="B190" s="11"/>
+      <c r="C190" s="5"/>
+      <c r="D190" s="12"/>
+      <c r="E190" s="16"/>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A191" s="11"/>
+      <c r="B191" s="11"/>
+      <c r="C191" s="5"/>
+      <c r="D191" s="12"/>
+      <c r="E191" s="16"/>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A192" s="11"/>
+      <c r="B192" s="11"/>
+      <c r="C192" s="5"/>
+      <c r="D192" s="12"/>
+      <c r="E192" s="16"/>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A193" s="11"/>
+      <c r="B193" s="11"/>
+      <c r="C193" s="5"/>
+      <c r="D193" s="12"/>
+      <c r="E193" s="16"/>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A194" s="11"/>
+      <c r="B194" s="11"/>
+      <c r="C194" s="5"/>
+      <c r="D194" s="12"/>
+      <c r="E194" s="16"/>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A195" s="11"/>
+      <c r="B195" s="11"/>
+      <c r="C195" s="5"/>
+      <c r="D195" s="12"/>
+      <c r="E195" s="16"/>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A196" s="11"/>
+      <c r="B196" s="11"/>
+      <c r="C196" s="5"/>
+      <c r="D196" s="12"/>
+      <c r="E196" s="16"/>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A197" s="11"/>
+      <c r="B197" s="11"/>
+      <c r="C197" s="5"/>
+      <c r="D197" s="12"/>
+      <c r="E197" s="16"/>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A198" s="11"/>
+      <c r="B198" s="11"/>
+      <c r="C198" s="5"/>
+      <c r="D198" s="12"/>
+      <c r="E198" s="16"/>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A199" s="11"/>
+      <c r="B199" s="11"/>
+      <c r="C199" s="5"/>
+      <c r="D199" s="12"/>
+      <c r="E199" s="16"/>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A200" s="11"/>
+      <c r="B200" s="11"/>
+      <c r="C200" s="5"/>
+      <c r="D200" s="12"/>
+      <c r="E200" s="16"/>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A201" s="11"/>
+      <c r="B201" s="11"/>
+      <c r="C201" s="5"/>
+      <c r="D201" s="12"/>
+      <c r="E201" s="16"/>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A202" s="11"/>
+      <c r="B202" s="11"/>
+      <c r="C202" s="5"/>
+      <c r="D202" s="12"/>
+      <c r="E202" s="16"/>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A203" s="11"/>
+      <c r="B203" s="11"/>
+      <c r="C203" s="5"/>
+      <c r="D203" s="12"/>
+      <c r="E203" s="16"/>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A204" s="11"/>
+      <c r="B204" s="11"/>
+      <c r="C204" s="5"/>
+      <c r="D204" s="12"/>
+      <c r="E204" s="16"/>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A205" s="11"/>
+      <c r="B205" s="11"/>
+      <c r="C205" s="5"/>
+      <c r="D205" s="12"/>
+      <c r="E205" s="16"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A206" s="11"/>
+      <c r="B206" s="11"/>
+      <c r="C206" s="5"/>
+      <c r="D206" s="12"/>
+      <c r="E206" s="16"/>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A207" s="11"/>
+      <c r="B207" s="11"/>
+      <c r="C207" s="5"/>
+      <c r="D207" s="12"/>
+      <c r="E207" s="16"/>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A208" s="11"/>
+      <c r="B208" s="11"/>
+      <c r="C208" s="5"/>
+      <c r="D208" s="12"/>
+      <c r="E208" s="16"/>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A209" s="11"/>
+      <c r="B209" s="11"/>
+      <c r="C209" s="5"/>
+      <c r="D209" s="12"/>
+      <c r="E209" s="16"/>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A210" s="11"/>
+      <c r="B210" s="11"/>
+      <c r="C210" s="5"/>
+      <c r="D210" s="12"/>
+      <c r="E210" s="16"/>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A211" s="11"/>
+      <c r="B211" s="11"/>
+      <c r="C211" s="5"/>
+      <c r="D211" s="12"/>
+      <c r="E211" s="16"/>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A212" s="11"/>
+      <c r="B212" s="11"/>
+      <c r="C212" s="5"/>
+      <c r="D212" s="12"/>
+      <c r="E212" s="16"/>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A213" s="11"/>
+      <c r="B213" s="11"/>
+      <c r="C213" s="5"/>
+      <c r="D213" s="12"/>
+      <c r="E213" s="16"/>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A214" s="11"/>
+      <c r="B214" s="11"/>
+      <c r="C214" s="5"/>
+      <c r="D214" s="12"/>
+      <c r="E214" s="16"/>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C215" s="17"/>
+      <c r="D215" s="18"/>
+      <c r="E215" s="16"/>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C216" s="17"/>
+      <c r="D216" s="18"/>
+      <c r="E216" s="16"/>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C217" s="17"/>
+      <c r="D217" s="18"/>
+      <c r="E217" s="16"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C218" s="17"/>
+      <c r="D218" s="18"/>
+      <c r="E218" s="16"/>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C219" s="17"/>
+      <c r="D219" s="18"/>
+      <c r="E219" s="16"/>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C220" s="17"/>
+      <c r="D220" s="18"/>
+      <c r="E220" s="16"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C221" s="17"/>
+      <c r="D221" s="18"/>
+      <c r="E221" s="16"/>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C222" s="17"/>
+      <c r="D222" s="18"/>
+      <c r="E222" s="16"/>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C223" s="17"/>
+      <c r="D223" s="18"/>
+      <c r="E223" s="16"/>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C224" s="17"/>
+      <c r="D224" s="18"/>
+      <c r="E224" s="16"/>
+    </row>
+    <row r="225" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C225" s="17"/>
+      <c r="D225" s="18"/>
+      <c r="E225" s="16"/>
+    </row>
+    <row r="226" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C226" s="17"/>
+      <c r="D226" s="18"/>
+      <c r="E226" s="16"/>
+    </row>
+    <row r="227" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C227" s="17"/>
+      <c r="D227" s="18"/>
+      <c r="E227" s="16"/>
+    </row>
+    <row r="228" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C228" s="17"/>
+      <c r="D228" s="18"/>
+      <c r="E228" s="16"/>
+    </row>
+    <row r="229" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C229" s="17"/>
+      <c r="D229" s="18"/>
+      <c r="E229" s="16"/>
+    </row>
+    <row r="230" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C230" s="17"/>
+      <c r="D230" s="18"/>
+      <c r="E230" s="16"/>
+    </row>
+    <row r="231" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C231" s="17"/>
+      <c r="D231" s="18"/>
+      <c r="E231" s="16"/>
+    </row>
+    <row r="232" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C232" s="17"/>
+      <c r="D232" s="18"/>
+      <c r="E232" s="16"/>
+    </row>
+    <row r="233" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C233" s="17"/>
+      <c r="D233" s="18"/>
+      <c r="E233" s="16"/>
+    </row>
+    <row r="234" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C234" s="17"/>
+      <c r="D234" s="18"/>
+      <c r="E234" s="16"/>
+    </row>
+    <row r="235" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C235" s="17"/>
+      <c r="D235" s="18"/>
+      <c r="E235" s="16"/>
+    </row>
+    <row r="236" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C236" s="17"/>
+      <c r="D236" s="18"/>
+      <c r="E236" s="16"/>
+    </row>
+    <row r="237" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C237" s="17"/>
+      <c r="D237" s="18"/>
+      <c r="E237" s="16"/>
+    </row>
+    <row r="238" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C238" s="17"/>
+      <c r="D238" s="18"/>
+      <c r="E238" s="16"/>
+    </row>
+    <row r="239" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C239" s="17"/>
+      <c r="D239" s="18"/>
+      <c r="E239" s="16"/>
+    </row>
+    <row r="240" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C240" s="17"/>
+      <c r="D240" s="18"/>
+      <c r="E240" s="16"/>
+    </row>
+    <row r="241" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C241" s="17"/>
+      <c r="D241" s="18"/>
+      <c r="E241" s="16"/>
+    </row>
+    <row r="242" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C242" s="17"/>
+      <c r="D242" s="18"/>
+      <c r="E242" s="16"/>
+    </row>
+    <row r="243" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C243" s="17"/>
+      <c r="D243" s="18"/>
+      <c r="E243" s="16"/>
+    </row>
+    <row r="244" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C244" s="17"/>
+      <c r="D244" s="18"/>
+      <c r="E244" s="16"/>
+    </row>
+    <row r="245" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C245" s="17"/>
+      <c r="D245" s="18"/>
+      <c r="E245" s="16"/>
+    </row>
+    <row r="246" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C246" s="17"/>
+      <c r="D246" s="18"/>
+      <c r="E246" s="16"/>
+    </row>
+    <row r="247" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C247" s="17"/>
+      <c r="D247" s="18"/>
+      <c r="E247" s="16"/>
+    </row>
+    <row r="248" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C248" s="17"/>
+      <c r="D248" s="18"/>
+      <c r="E248" s="16"/>
+    </row>
+    <row r="249" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C249" s="17"/>
+      <c r="D249" s="18"/>
+      <c r="E249" s="16"/>
+    </row>
+    <row r="250" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C250" s="17"/>
+      <c r="D250" s="18"/>
+      <c r="E250" s="16"/>
+    </row>
+    <row r="251" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C251" s="17"/>
+      <c r="D251" s="18"/>
+      <c r="E251" s="16"/>
+    </row>
+    <row r="252" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C252" s="17"/>
+      <c r="D252" s="18"/>
+      <c r="E252" s="16"/>
+    </row>
+    <row r="253" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C253" s="17"/>
+      <c r="D253" s="18"/>
+      <c r="E253" s="16"/>
+    </row>
+    <row r="254" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C254" s="17"/>
+      <c r="D254" s="18"/>
+      <c r="E254" s="16"/>
+    </row>
+    <row r="255" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C255" s="17"/>
+      <c r="D255" s="18"/>
+      <c r="E255" s="16"/>
+    </row>
+    <row r="256" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C256" s="17"/>
+      <c r="D256" s="18"/>
+      <c r="E256" s="16"/>
+    </row>
+    <row r="257" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C257" s="17"/>
+      <c r="D257" s="18"/>
+      <c r="E257" s="16"/>
+    </row>
+    <row r="258" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C258" s="17"/>
+      <c r="D258" s="18"/>
+      <c r="E258" s="16"/>
+    </row>
+    <row r="259" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C259" s="17"/>
+      <c r="D259" s="18"/>
+      <c r="E259" s="16"/>
+    </row>
+    <row r="260" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C260" s="17"/>
+      <c r="D260" s="18"/>
+      <c r="E260" s="16"/>
+    </row>
+    <row r="261" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C261" s="17"/>
+      <c r="D261" s="18"/>
+      <c r="E261" s="16"/>
+    </row>
+    <row r="262" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C262" s="17"/>
+      <c r="D262" s="18"/>
+      <c r="E262" s="16"/>
+    </row>
+    <row r="263" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C263" s="17"/>
+      <c r="D263" s="18"/>
+      <c r="E263" s="16"/>
+    </row>
+    <row r="264" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C264" s="17"/>
+      <c r="D264" s="18"/>
+      <c r="E264" s="16"/>
+    </row>
+    <row r="265" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C265" s="17"/>
+      <c r="D265" s="18"/>
+      <c r="E265" s="16"/>
+    </row>
+    <row r="266" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C266" s="17"/>
+      <c r="D266" s="18"/>
+      <c r="E266" s="16"/>
+    </row>
+    <row r="267" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C267" s="17"/>
+      <c r="D267" s="18"/>
+      <c r="E267" s="16"/>
+    </row>
+    <row r="268" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C268" s="17"/>
+      <c r="D268" s="18"/>
+      <c r="E268" s="16"/>
+    </row>
+    <row r="269" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C269" s="17"/>
+      <c r="D269" s="18"/>
+      <c r="E269" s="16"/>
+    </row>
+    <row r="270" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C270" s="17"/>
+      <c r="D270" s="18"/>
+      <c r="E270" s="16"/>
+    </row>
+    <row r="271" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C271" s="17"/>
+      <c r="D271" s="18"/>
+      <c r="E271" s="16"/>
+    </row>
+    <row r="272" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C272" s="17"/>
+      <c r="D272" s="18"/>
+      <c r="E272" s="16"/>
+    </row>
+    <row r="273" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C273" s="17"/>
+      <c r="D273" s="18"/>
+      <c r="E273" s="16"/>
+    </row>
+    <row r="274" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C274" s="17"/>
+      <c r="D274" s="18"/>
+      <c r="E274" s="16"/>
+    </row>
+    <row r="275" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C275" s="17"/>
+      <c r="D275" s="18"/>
+      <c r="E275" s="16"/>
+    </row>
+    <row r="276" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C276" s="17"/>
+      <c r="D276" s="18"/>
+      <c r="E276" s="16"/>
+    </row>
+    <row r="277" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C277" s="17"/>
+      <c r="D277" s="18"/>
+      <c r="E277" s="16"/>
+    </row>
+    <row r="278" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C278" s="17"/>
+      <c r="D278" s="18"/>
+      <c r="E278" s="16"/>
+    </row>
+    <row r="279" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C279" s="17"/>
+      <c r="D279" s="18"/>
+      <c r="E279" s="16"/>
+    </row>
+    <row r="280" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C280" s="17"/>
+      <c r="D280" s="18"/>
+      <c r="E280" s="16"/>
+    </row>
+    <row r="281" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C281" s="17"/>
+      <c r="D281" s="18"/>
+      <c r="E281" s="16"/>
+    </row>
+    <row r="282" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C282" s="17"/>
+      <c r="D282" s="18"/>
+      <c r="E282" s="16"/>
+    </row>
+    <row r="283" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C283" s="17"/>
+      <c r="D283" s="18"/>
+      <c r="E283" s="16"/>
+    </row>
+    <row r="284" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C284" s="17"/>
+      <c r="D284" s="18"/>
+      <c r="E284" s="16"/>
+    </row>
+    <row r="285" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C285" s="17"/>
+      <c r="D285" s="18"/>
+      <c r="E285" s="16"/>
+    </row>
+    <row r="286" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C286" s="17"/>
+      <c r="D286" s="18"/>
+      <c r="E286" s="16"/>
+    </row>
+    <row r="287" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C287" s="17"/>
+      <c r="D287" s="18"/>
+      <c r="E287" s="16"/>
+    </row>
+    <row r="288" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C288" s="17"/>
+      <c r="D288" s="18"/>
+      <c r="E288" s="16"/>
+    </row>
+    <row r="289" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C289" s="17"/>
+      <c r="D289" s="18"/>
+      <c r="E289" s="16"/>
+    </row>
+    <row r="290" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C290" s="17"/>
+      <c r="D290" s="18"/>
+      <c r="E290" s="16"/>
+    </row>
+    <row r="291" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C291" s="17"/>
+      <c r="D291" s="18"/>
+      <c r="E291" s="16"/>
+    </row>
+    <row r="292" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C292" s="17"/>
+      <c r="D292" s="18"/>
+      <c r="E292" s="16"/>
+    </row>
+    <row r="293" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C293" s="17"/>
+      <c r="D293" s="18"/>
+      <c r="E293" s="16"/>
+    </row>
+    <row r="294" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C294" s="17"/>
+      <c r="D294" s="18"/>
+      <c r="E294" s="16"/>
+    </row>
+    <row r="295" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C295" s="17"/>
+      <c r="D295" s="18"/>
+      <c r="E295" s="16"/>
+    </row>
+    <row r="296" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C296" s="17"/>
+      <c r="D296" s="18"/>
+      <c r="E296" s="16"/>
+    </row>
+    <row r="297" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C297" s="17"/>
+      <c r="D297" s="18"/>
+      <c r="E297" s="16"/>
+    </row>
+    <row r="298" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C298" s="17"/>
+      <c r="D298" s="18"/>
+      <c r="E298" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
@@ -14648,12 +15917,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14822,15 +16088,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF4E6923-AA8C-46B2-BFD7-28436A9FBB54}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AB9CE81-3049-4EF8-B575-56E5C1922046}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14855,10 +16125,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AB9CE81-3049-4EF8-B575-56E5C1922046}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF4E6923-AA8C-46B2-BFD7-28436A9FBB54}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>